--- a/InputData/land/CApULAbIFM/CO2 Abated per Unit Land Area by Impr For Mgmt.xlsx
+++ b/InputData/land/CApULAbIFM/CO2 Abated per Unit Land Area by Impr For Mgmt.xlsx
@@ -1,23 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27615"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\land\CApULAbIFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deept\Dropbox\EPS\Input Data for India 2.0\land\CApULAbIFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF08A53-F280-4704-83EC-0E3DACD573C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1FD453C-C493-4734-BC10-DC4B82D5AA15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="CApULAbIFM" sheetId="3" r:id="rId2"/>
+    <sheet name="Calculations" sheetId="4" r:id="rId2"/>
+    <sheet name="CApULAbIFM" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -25,6 +29,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,28 +38,146 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>CApULAbIFM CO2 Abated per Unit Land Area by Improved Forest Management</t>
   </si>
   <si>
-    <t>Source:</t>
+    <t>Source 1:</t>
+  </si>
+  <si>
+    <t>Enhanced Carbon Stocks Achievable by Improved Forest Management</t>
+  </si>
+  <si>
+    <t>GHGPI Phase III Emissions Estimates AFOLU sector (2005 - 2015)</t>
+  </si>
+  <si>
+    <t>Indian Council of Forestry Research and Education</t>
+  </si>
+  <si>
+    <t>GHGPI Platform India - Vasudha Foundation</t>
+  </si>
+  <si>
+    <t>Singh,Tajinder Pal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dhingra, S., Singh, D., and Mehta, R. </t>
+  </si>
+  <si>
+    <t>http://web.archive.org/web/20170918224752/http://www.teriuniversity.ac.in/mct/pdf/assignment/TP-Singh.pdf</t>
+  </si>
+  <si>
+    <t>http://www.ghgplatform-india.org/afolu-sector</t>
+  </si>
+  <si>
+    <t>Conservation and Enhancement of Forest Carbon Stocks</t>
+  </si>
+  <si>
+    <t>Sheets: Forest Area, Forest Change Matrix</t>
+  </si>
+  <si>
+    <t>India’s proposed Modified Submission on Forest Reference Levels for REDD+ 
+Result based Payments under UNFCCC</t>
+  </si>
+  <si>
+    <t>MoEF</t>
+  </si>
+  <si>
+    <t>https://redd.unfccc.int/files/modified_submission_of_frl_02_november_2018.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The India-specific source available is from 2012, where the change in carbon stock  </t>
+  </si>
+  <si>
+    <t>and change in area is estimated across management practices (Source 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">While more recent data on change in carbon stock and forest area is available in </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GHGPI's database (for 2015) (Source 2), it is not diversifed in terms of forest </t>
+  </si>
+  <si>
+    <t>management activities. Hence, we use the 2012 estimates from the ICFRE study</t>
+  </si>
+  <si>
+    <t>We take a weighted average of the forest types.</t>
+  </si>
+  <si>
+    <t>Another official source on India's Submission (modified) on Forest Reference Levels for REDD+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">However, this only states the baseline stocks and not incremental stocks from improved  </t>
+  </si>
+  <si>
+    <t>forest management practices (Source 3)</t>
+  </si>
+  <si>
+    <t>Increased Annual CO2 Sequestration Achievable by Improved Management Practices per Acre</t>
+  </si>
+  <si>
+    <t>Forest Type</t>
+  </si>
+  <si>
+    <t>Area (ha)</t>
+  </si>
+  <si>
+    <t>Area (acres)</t>
+  </si>
+  <si>
+    <t>Enhanced Carbon Stocks (tCO2-e per year)</t>
+  </si>
+  <si>
+    <t>Enhanced Carbon Stocks by area (tCO2-e per year/acre)</t>
+  </si>
+  <si>
+    <t>Restoration of Moderately Dense</t>
+  </si>
+  <si>
+    <t>Restoration of Open Forests</t>
+  </si>
+  <si>
+    <t>Restoration of scrub and grassland</t>
+  </si>
+  <si>
+    <t>Enhancement of Mangroves</t>
+  </si>
+  <si>
+    <t>Enhancing Urban Areas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agro-forestry </t>
+  </si>
+  <si>
+    <t>Weighted Average</t>
+  </si>
+  <si>
+    <t>Weighted Average CO2 Abatement Achievable by Improved Management Practices per Acre</t>
+  </si>
+  <si>
+    <t>g CO2 / acre / yr</t>
+  </si>
+  <si>
+    <t>Average, converted to grams CO2</t>
+  </si>
+  <si>
+    <t>Per Acre</t>
   </si>
   <si>
     <t>CO2 Abated (g)</t>
-  </si>
-  <si>
-    <t>Per Acre</t>
-  </si>
-  <si>
-    <t>consultation with American Forest Foundation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -69,13 +193,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -87,19 +225,32 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -116,9 +267,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -156,9 +307,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -191,26 +342,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -243,26 +377,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -436,57 +553,552 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K27"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="11" max="11" width="73.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="14.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="J3" s="10">
+        <v>2</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1"/>
+      <c r="B4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-    </row>
-    <row r="6" spans="1:2" ht="14.45" x14ac:dyDescent="0.35"/>
+      <c r="K4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1"/>
+      <c r="B5" s="4">
+        <v>2012</v>
+      </c>
+      <c r="K5" s="4">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="1"/>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="1"/>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="K8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="30">
+      <c r="J11" s="10">
+        <v>3</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="K12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="K13" s="4">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="K14" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="K15" s="9"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="K7" r:id="rId1" xr:uid="{8A9735FE-1BEE-4470-9D8C-6D01625B79BA}"/>
+    <hyperlink ref="K14" r:id="rId2" xr:uid="{F72DA327-12DB-461E-A6E3-29AA55656005}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="38.5703125" customWidth="1"/>
+    <col min="5" max="5" width="49.28515625" customWidth="1"/>
+    <col min="6" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="5">
+        <v>2000000</v>
+      </c>
+      <c r="C3">
+        <f>B3*2.47105</f>
+        <v>4942100</v>
+      </c>
+      <c r="D3" s="5">
+        <v>2930000</v>
+      </c>
+      <c r="E3" s="6">
+        <f>D3/C3</f>
+        <v>0.5928653811132919</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="5">
+        <v>4000000</v>
+      </c>
+      <c r="C4">
+        <f t="shared" ref="C4:C8" si="0">B4*2.47105</f>
+        <v>9884200</v>
+      </c>
+      <c r="D4" s="5">
+        <v>22000000</v>
+      </c>
+      <c r="E4" s="6">
+        <f t="shared" ref="E4:E8" si="1">D4/C4</f>
+        <v>2.2257744683434169</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="5">
+        <v>1200000</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>2965260</v>
+      </c>
+      <c r="D5" s="5">
+        <v>5100000</v>
+      </c>
+      <c r="E5" s="6">
+        <f t="shared" si="1"/>
+        <v>1.7199166346290038</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="5">
+        <v>100000</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>247105</v>
+      </c>
+      <c r="D6" s="5">
+        <v>910000</v>
+      </c>
+      <c r="E6" s="6">
+        <f t="shared" si="1"/>
+        <v>3.6826450294409261</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="5">
+        <v>200000</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>494210</v>
+      </c>
+      <c r="D7" s="5">
+        <v>220000</v>
+      </c>
+      <c r="E7" s="6">
+        <f t="shared" si="1"/>
+        <v>0.44515489366868333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="5">
+        <v>1500000</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>3706575</v>
+      </c>
+      <c r="D8" s="5">
+        <v>8140000</v>
+      </c>
+      <c r="E8" s="6">
+        <f t="shared" si="1"/>
+        <v>2.1960974754321714</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="D10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="6">
+        <f>SUMPRODUCT(E3:E8,D3:D8)/SUM(D3:D8)</f>
+        <v>2.0560072063674619</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3">
+        <f>E10*1000000</f>
+        <v>2056007.2063674619</v>
+      </c>
+      <c r="B13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="B1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="B2" s="3">
-        <f>1.5*10^6</f>
-        <v>1500000</v>
+        <f>Calculations!A13</f>
+        <v>2056007.2063674619</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="77cd1fc208aa16a525090c2a27f33c66">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d77402130d0e9b5bbfbb66ed18db98d9" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7231805-BA79-4251-9269-50D062E0A1BC}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7258275-396F-48F6-BA48-9A1C901E5A73}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B75A2A3-6F51-4E70-8733-F2559A6DF7D2}"/>
 </file>